--- a/AAII_Financials/Yearly/CMCM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CMCM_YR_FIN.xlsx
@@ -1014,7 +1014,7 @@
         <v>36900</v>
       </c>
       <c r="F14" s="3">
-        <v>66400</v>
+        <v>73700</v>
       </c>
       <c r="G14" s="3">
         <v>35700</v>
@@ -1257,7 +1257,7 @@
         <v>6200</v>
       </c>
       <c r="F20" s="3">
-        <v>2600</v>
+        <v>-4700</v>
       </c>
       <c r="G20" s="3">
         <v>15900</v>
@@ -1308,7 +1308,7 @@
         <v>-38100</v>
       </c>
       <c r="F21" s="3">
-        <v>-27100</v>
+        <v>-19800</v>
       </c>
       <c r="G21" s="3">
         <v>-41000</v>
@@ -1869,7 +1869,7 @@
         <v>-6200</v>
       </c>
       <c r="F32" s="3">
-        <v>-2600</v>
+        <v>4700</v>
       </c>
       <c r="G32" s="3">
         <v>-15900</v>
